--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC_30.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC_30.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB45C447-FA0E-4ADC-8082-848F1040717E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805202B6-22F3-4A14-9581-10A04435B620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2208" yWindow="1944" windowWidth="17280" windowHeight="9972" firstSheet="17" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9972" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PayNowCCNoCF" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="54">
   <si>
     <t>Result</t>
   </si>
@@ -141,33 +141,6 @@
     <t>14</t>
   </si>
   <si>
-    <t>Fri Jun 05 22:49:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:00:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:16:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:21:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:26:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:30:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:35:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 00:15:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 00:35:10 IST 2026</t>
-  </si>
-  <si>
     <t>Sat Jun 06 00:48:04 IST 2026</t>
   </si>
   <si>
@@ -189,29 +162,55 @@
     <t>Sat Jun 06 01:28:19 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jun 08 19:19:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 08 19:51:58 IST 2026</t>
-  </si>
-  <si>
-    <t>6432</t>
-  </si>
-  <si>
-    <t>6114</t>
-  </si>
-  <si>
-    <t>6115</t>
-  </si>
-  <si>
-    <t>Thu Jul 16 20:59:14 IST 2026</t>
+    <t>Wed Aug 19 08:01:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 08:57:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 09:47:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 10:39:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 11:28:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 11:44:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 10:11:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:02:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:17:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:22:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 12:07:18 IST 2026</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>985</t>
+  </si>
+  <si>
+    <t>986</t>
+  </si>
+  <si>
+    <t>12/31/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -594,11 +593,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>37</v>
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -688,11 +687,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>32</v>
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -737,7 +736,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
+    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -785,11 +784,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>33</v>
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -817,7 +816,7 @@
         <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -881,11 +880,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>39</v>
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -975,11 +974,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>40</v>
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1069,11 +1068,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>48</v>
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1163,11 +1162,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>49</v>
+      <c r="B2" t="s">
+        <v>42</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1257,11 +1256,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>42</v>
+      <c r="B2" t="s">
+        <v>33</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1353,11 +1352,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>43</v>
+      <c r="B2" t="s">
+        <v>34</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1449,11 +1448,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>44</v>
+      <c r="B2" t="s">
+        <v>35</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1545,11 +1544,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>45</v>
+      <c r="B2" t="s">
+        <v>36</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1596,7 +1595,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
+    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1644,10 +1643,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="2"/>
@@ -1740,11 +1739,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>34</v>
+      <c r="B2" t="s">
+        <v>47</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1836,11 +1835,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>35</v>
+      <c r="B2" t="s">
+        <v>48</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1932,11 +1931,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>46</v>
+      <c r="B2" t="s">
+        <v>37</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2024,11 +2023,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>53</v>
+      <c r="B2" t="s">
+        <v>40</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2118,11 +2117,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>47</v>
+      <c r="B2" t="s">
+        <v>38</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2212,11 +2211,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>36</v>
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2306,11 +2305,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>41</v>
+      <c r="B2" t="s">
+        <v>32</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC_30.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC_30.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
@@ -35,7 +35,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="106">
   <si>
     <t>Result</t>
   </si>
@@ -205,12 +205,169 @@
   </si>
   <si>
     <t>12/31/2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:09:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:15:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:21:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:27:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:32:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:37:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:43:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:51:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:53:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:54:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:56:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:22:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:23:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:25:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:26:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:34:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:36:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:52:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:55:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:19:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:28:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:33:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:36:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:40:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:41:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 20:04:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 20:09:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:22:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:29:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:43:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:50:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:03:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:22:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:27:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:33:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:34:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:36:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:38:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:44:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:02:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:23:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:27:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:31:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:39:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:42:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:45:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:48:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:51:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:53:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 04:06:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 20:27:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 20:43:58 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -593,11 +750,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>39</v>
+      <c r="A2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>85</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -687,11 +844,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>45</v>
+      <c r="A2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>104</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -736,7 +893,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -784,11 +941,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>46</v>
+      <c r="A2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>81</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -880,11 +1037,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>43</v>
+      <c r="A2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>92</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -974,11 +1131,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>44</v>
+      <c r="A2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>93</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1068,11 +1225,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>41</v>
+      <c r="A2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>87</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1162,11 +1319,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>42</v>
+      <c r="B2" t="s" s="0">
+        <v>105</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1256,11 +1413,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
+      <c r="B2" t="s" s="0">
+        <v>95</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1352,11 +1509,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>34</v>
+      <c r="B2" t="s" s="0">
+        <v>96</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1448,11 +1605,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>35</v>
+      <c r="B2" t="s" s="0">
+        <v>97</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1544,11 +1701,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>36</v>
+      <c r="B2" t="s" s="0">
+        <v>98</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1595,7 +1752,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1643,10 +1800,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>25</v>
       </c>
       <c r="C2" s="2"/>
@@ -1739,11 +1896,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
+      <c r="B2" t="s" s="0">
+        <v>82</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1835,11 +1992,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
+      <c r="B2" t="s" s="0">
+        <v>83</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1931,11 +2088,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>37</v>
+      <c r="B2" t="s" s="0">
+        <v>102</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2023,11 +2180,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
+      <c r="A2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>86</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2117,11 +2274,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>38</v>
+      <c r="B2" t="s" s="0">
+        <v>103</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2211,11 +2368,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
+      <c r="A2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>84</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2305,11 +2462,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>32</v>
+      <c r="B2" t="s" s="0">
+        <v>94</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
